--- a/apps/api/assets/vocabulary/初中/外研版/外研版初中英语七年级下册.xlsx
+++ b/apps/api/assets/vocabulary/初中/外研版/外研版初中英语七年级下册.xlsx
@@ -440,7 +440,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D446"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
@@ -613,6 +613,16 @@
           <t>first of all</t>
         </is>
       </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 第一
@@ -673,6 +683,16 @@
       <c r="A11" s="2" t="inlineStr">
         <is>
           <t>lost and found box</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -831,6 +851,16 @@
           <t>be careful with</t>
         </is>
       </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">v. 注意；照顾
@@ -869,6 +899,16 @@
           <t>from now on</t>
         </is>
       </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 从今以后
@@ -882,6 +922,16 @@
           <t>here is ...</t>
         </is>
       </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 这是；是简单的倒装句；在这里</t>
@@ -892,6 +942,16 @@
       <c r="A22" s="2" t="inlineStr">
         <is>
           <t>here are ...</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -954,6 +1014,16 @@
           <t>mobile phone</t>
         </is>
       </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">n. 手机；移动电话
@@ -967,6 +1037,16 @@
           <t>lost and found office</t>
         </is>
       </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
           <t>失物招领处</t>
@@ -977,6 +1057,16 @@
       <c r="A27" s="2" t="inlineStr">
         <is>
           <t>in a hurry</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1135,6 +1225,16 @@
           <t>hundreds of</t>
         </is>
       </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 好几百
@@ -1483,6 +1583,16 @@
           <t>would like</t>
         </is>
       </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">v. 想要
@@ -1548,6 +1658,16 @@
           <t>that's all</t>
         </is>
       </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 就这样；仅此而已；一三国际</t>
@@ -1584,6 +1704,16 @@
           <t>worry about</t>
         </is>
       </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">v. 发愁；担忧；为…发愁；替…担忧
@@ -1691,6 +1821,16 @@
       <c r="A59" s="2" t="inlineStr">
         <is>
           <t>get on well with sb.</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -1731,6 +1871,16 @@
           <t>ready to do sth.</t>
         </is>
       </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 愿意做某事；准备好要做没某事；准备去做某事</t>
@@ -2039,6 +2189,16 @@
       <c r="A74" s="2" t="inlineStr">
         <is>
           <t>just like</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -2419,6 +2579,16 @@
           <t>look forward to</t>
         </is>
       </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 盼望
@@ -2457,6 +2627,16 @@
           <t>make friends</t>
         </is>
       </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 交朋友；交友；结交朋友</t>
@@ -2587,6 +2767,16 @@
           <t>enjoy oneself</t>
         </is>
       </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 过得快乐
@@ -2665,6 +2855,16 @@
       <c r="A102" s="2" t="inlineStr">
         <is>
           <t>May Day</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
@@ -2726,6 +2926,16 @@
       <c r="A105" s="2" t="inlineStr">
         <is>
           <t>take a walk</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
@@ -2866,6 +3076,16 @@
           <t>summer holiday</t>
         </is>
       </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">n. 暑假
@@ -2949,6 +3169,16 @@
       <c r="A115" s="2" t="inlineStr">
         <is>
           <t>go sightseeing</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
@@ -3154,6 +3384,16 @@
           <t>in the future</t>
         </is>
       </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">adv. 今后
@@ -3381,6 +3621,16 @@
           <t>be able to</t>
         </is>
       </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">v. 能够
@@ -3420,6 +3670,16 @@
           <t>not ... any more</t>
         </is>
       </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">adv. 不再
@@ -3770,6 +4030,16 @@
           <t>here is ...</t>
         </is>
       </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 这是；是简单的倒装句；在这里</t>
@@ -3780,6 +4050,16 @@
       <c r="A152" s="2" t="inlineStr">
         <is>
           <t>here are ...</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
@@ -3909,6 +4189,16 @@
       <c r="A158" s="2" t="inlineStr">
         <is>
           <t>not only ... but also ...</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D158" s="2" t="inlineStr">
@@ -4283,6 +4573,16 @@
           <t>Mother's Day</t>
         </is>
       </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D174" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. (美国和加拿大的)母亲节
@@ -4392,6 +4692,16 @@
           <t>try on</t>
         </is>
       </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D179" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 试穿；〈非正式〉搞恶作剧(以试探能否被容忍)；〈非正式〉耍花招
@@ -4425,6 +4735,16 @@
       <c r="A181" s="2" t="inlineStr">
         <is>
           <t>wait a minute</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D181" s="2" t="inlineStr">
@@ -4863,6 +5183,16 @@
       <c r="A200" s="2" t="inlineStr">
         <is>
           <t>one of</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D200" s="2" t="inlineStr">
@@ -5001,6 +5331,16 @@
           <t>go out</t>
         </is>
       </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D206" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 出去；灭；辞职；下台
@@ -5038,6 +5378,16 @@
       <c r="A208" s="2" t="inlineStr">
         <is>
           <t>one day</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D208" s="2" t="inlineStr">
@@ -5436,6 +5786,16 @@
       <c r="A225" s="2" t="inlineStr">
         <is>
           <t>Why not ... ?</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D225" s="2" t="inlineStr">
@@ -6127,6 +6487,16 @@
           <t>primary school</t>
         </is>
       </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D254" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">n. 小学
@@ -6490,6 +6860,16 @@
       <c r="A270" s="2" t="inlineStr">
         <is>
           <t>movie theater</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D270" s="2" t="inlineStr">
@@ -6767,6 +7147,16 @@
           <t>once upon a time</t>
         </is>
       </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D282" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 从前；很久很久以前；古时候
@@ -6801,6 +7191,16 @@
       <c r="A284" s="2" t="inlineStr">
         <is>
           <t>go for a walk</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D284" s="2" t="inlineStr">
@@ -6863,6 +7263,16 @@
           <t>all alone</t>
         </is>
       </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D287" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 仅仅一个人；独力
@@ -6923,6 +7333,16 @@
       <c r="A290" s="2" t="inlineStr">
         <is>
           <t>pick up</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D290" s="2" t="inlineStr">
@@ -7318,6 +7738,16 @@
           <t>in pieces</t>
         </is>
       </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D307" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 破碎；(意见等)分歧
@@ -7401,6 +7831,16 @@
       <c r="A311" s="2" t="inlineStr">
         <is>
           <t>at first</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D311" s="2" t="inlineStr">
@@ -7630,6 +8070,16 @@
           <t>Women's Day</t>
         </is>
       </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D321" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 妇女节；国际劳动妇女节；三八妇女节</t>
@@ -7642,6 +8092,16 @@
           <t>National Day</t>
         </is>
       </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D322" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 国庆日
@@ -7655,6 +8115,16 @@
           <t>Children's Day</t>
         </is>
       </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D323" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 儿童节
@@ -7821,6 +8291,16 @@
       <c r="A331" s="2" t="inlineStr">
         <is>
           <t>find out</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D331" s="2" t="inlineStr">
@@ -7861,6 +8341,16 @@
           <t>at the age of</t>
         </is>
       </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D333" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 在…岁时
@@ -7970,6 +8460,16 @@
           <t>in the 1860s</t>
         </is>
       </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D338" s="2" t="inlineStr">
         <is>
           <t>无</t>
@@ -8242,6 +8742,16 @@
       <c r="A350" s="2" t="inlineStr">
         <is>
           <t>around the world</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D350" s="2" t="inlineStr">
@@ -9049,6 +9559,16 @@
           <t>each other</t>
         </is>
       </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D384" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">pron. 彼此
@@ -9345,6 +9865,16 @@
           <t>North American</t>
         </is>
       </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D397" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 北美洲的；北美公司；北美之神</t>
@@ -9404,6 +9934,16 @@
           <t>arm in arm</t>
         </is>
       </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D400" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 臂挽着臂
@@ -9415,6 +9955,16 @@
       <c r="A401" s="2" t="inlineStr">
         <is>
           <t>South American</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D401" s="2" t="inlineStr">
@@ -9501,6 +10051,16 @@
           <t>not at all</t>
         </is>
       </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D405" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 毫无(=〔美国英语〕 You are welcome)
@@ -9603,6 +10163,16 @@
       <c r="A410" s="2" t="inlineStr">
         <is>
           <t>in fact</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D410" s="2" t="inlineStr">
@@ -10249,6 +10819,16 @@
           <t>dance music</t>
         </is>
       </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D438" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">un. 舞曲
